--- a/data_processed/results_OLS_pkm_car_per_capitaincome.xlsx
+++ b/data_processed/results_OLS_pkm_car_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.5863" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.5912" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7499.036283276515</v>
+        <v>33.49865827112031</v>
       </c>
       <c r="D2" t="n">
-        <v>5.960224652935623e-50</v>
+        <v>0.6448802773162011</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>909.9689846837235</v>
+        <v>635.362570917376</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79.18019231708647</v>
+        <v>-1409.452350654927</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09204419583827038</v>
+        <v>1.715355461547352e-125</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-16.04054522186076</v>
+        <v>13.90342632822689</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3280730520520518</v>
+        <v>6.097586154895574e-14</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-873.8631364841974</v>
+        <v>-277.0416822800781</v>
       </c>
       <c r="D6" t="n">
-        <v>3.20296624764108e-154</v>
+        <v>8.136126983913873e-11</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.05606778055128164</v>
+        <v>7.035125524396507e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>2.110372726891547e-22</v>
+        <v>0.6882758200920889</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.2662219568566002</v>
+        <v>-0.3461057353023459</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009723296090734334</v>
+        <v>0.001439995143798476</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02878616216080822</v>
+        <v>0.202833258319848</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4012069221500646</v>
+        <v>7.005760032126643e-09</v>
       </c>
     </row>
     <row r="10">
@@ -579,46 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>cars_per_adult</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1340.910721215788</v>
+        <v>9573.930441237309</v>
       </c>
       <c r="D10" t="n">
-        <v>7.490962830204028e-49</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>dwelling_size</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>14.87796637607935</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3.505318778740015e-07</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cars_per_adult</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>109.6680589619041</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0006959941215086642</v>
+        <v>1.907369281195097e-164</v>
       </c>
     </row>
   </sheetData>
